--- a/business_surveys/046_vinegar_usage_survey--business_surveys.xlsx
+++ b/business_surveys/046_vinegar_usage_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apple_cider</t>
+          <t>apple cider</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>balsamic_vinegar</t>
+          <t>balsamic vinegar</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>white_wine</t>
+          <t>white wine</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>white_vinegar</t>
+          <t>white vinegar</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>every_day</t>
+          <t>every day</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>every_other_day</t>
+          <t>every other day</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>grocery_store</t>
+          <t>grocery store</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>health_food_store</t>
+          <t>health food store</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>specialty_food_store</t>
+          <t>specialty food store</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>very_often</t>
+          <t>very often</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>very_often</t>
+          <t>very often</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>grocery_store</t>
+          <t>grocery store</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>health_food_store</t>
+          <t>health food store</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>specialty_food_store</t>
+          <t>specialty food store</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>for_culinary_use</t>
+          <t>for culinary use</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>for_health_reasins</t>
+          <t>for health reasins</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>for_other</t>
+          <t>for other</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>for_specialty_use</t>
+          <t>for specialty use</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>for_other_reasons</t>
+          <t>for other reasons</t>
         </is>
       </c>
     </row>
